--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260803.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260803.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>78,307</t>
+          <t>78,007</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.88%</t>
+          <t>11.21%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>32,396</t>
+          <t>32,296</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.74%</t>
+          <t>10.66%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>35,555</t>
+          <t>35,455</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.94%</t>
+          <t>7.91%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>90,325</t>
+          <t>90,125</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.30%</t>
+          <t>7.77%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>195,156</t>
+          <t>194,656</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>5.53%</t>
         </is>
       </c>
     </row>
@@ -721,100 +721,100 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>103,791</t>
+          <t>103,491</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.36%</t>
+          <t>4.22%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>112,566</t>
+          <t>48,895</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.50%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>48,995</t>
+          <t>112,266</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.42%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>HUBB US</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>安柏</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>19,379</t>
+          <t>58,759</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>HUBB US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>安柏</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>58,959</t>
+          <t>19,279</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>117,083</t>
+          <t>116,783</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>54,227</t>
+          <t>54,127</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>136,301</t>
+          <t>135,901</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>22,531</t>
+          <t>22,431</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>24,304</t>
+          <t>24,204</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>62,303</t>
+          <t>62,103</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>36,780</t>
+          <t>36,680</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -985,56 +985,56 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>49,736</t>
+          <t>49,636</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>51,210</t>
+          <t>76,801</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>77,001</t>
+          <t>51,110</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>50,060</t>
+          <t>49,960</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>32,510</t>
+          <t>32,410</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1095,56 +1095,56 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>47,027</t>
+          <t>46,927</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>30,445</t>
+          <t>22,158</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>22,258</t>
+          <t>30,345</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>95,063</t>
+          <t>94,763</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>27,569</t>
+          <t>27,469</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1210,68 +1210,68 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>20,709</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>20,609</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>75,074</t>
+          <t>9,004</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,22 +1283,22 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,004</t>
+          <t>74,874</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1315,56 +1315,56 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>145,945</t>
+          <t>145,545</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>30,314</t>
+          <t>13,252</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>13,252</t>
+          <t>30,214</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>30,691</t>
+          <t>30,591</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>25,781</t>
+          <t>13,424</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,39 +1459,39 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>43,483</t>
+          <t>25,681</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>13,424</t>
+          <t>43,383</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>94,502</t>
+          <t>94,202</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>23,519</t>
+          <t>23,419</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>18,453</t>
+          <t>18,353</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>38,261</t>
+          <t>38,161</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>104,527,579</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
